--- a/data/trans_dic/Viv_Temp_insuf-Edad-trans_dic.xlsx
+++ b/data/trans_dic/Viv_Temp_insuf-Edad-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con temperatura insuficiente</t>
+          <t>Población con temperatura insuficiente, en verano o en invierno, en la vivienda (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,5; 6,28</t>
+          <t>2,57; 6,54</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,45; 20,23</t>
+          <t>12,33; 20,05</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,15; 18,44</t>
+          <t>5,98; 18,79</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,92; 7,15</t>
+          <t>2,96; 6,99</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>10,67; 18,08</t>
+          <t>10,65; 17,87</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,14; 14,91</t>
+          <t>4,27; 14,91</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,11; 5,83</t>
+          <t>3,08; 5,97</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>12,5; 17,7</t>
+          <t>12,77; 17,7</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,6; 14,67</t>
+          <t>6,5; 14,18</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,75; 7,66</t>
+          <t>3,4; 7,53</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>13,6; 19,79</t>
+          <t>13,16; 19,53</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,87; 17,49</t>
+          <t>8,92; 17,74</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,88; 4,53</t>
+          <t>1,89; 4,8</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>14,09; 20,03</t>
+          <t>14,06; 20,06</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,21; 53,14</t>
+          <t>10,43; 53,68</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,16; 5,49</t>
+          <t>3,23; 5,7</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>14,57; 19,12</t>
+          <t>14,67; 19,2</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11,14; 37,75</t>
+          <t>11,1; 38,11</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,77; 6,05</t>
+          <t>2,93; 6,15</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10,78; 16,43</t>
+          <t>10,75; 16,39</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10,03; 15,94</t>
+          <t>10,05; 15,89</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,69; 5,89</t>
+          <t>2,77; 6,04</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10,0; 15,13</t>
+          <t>10,28; 15,23</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,99; 12,09</t>
+          <t>6,78; 11,79</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,09; 5,29</t>
+          <t>3,17; 5,42</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11,11; 14,94</t>
+          <t>11,19; 14,85</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9,15; 13,15</t>
+          <t>9,1; 13,07</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,38; 5,75</t>
+          <t>2,25; 5,6</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>12,7; 19,07</t>
+          <t>13,1; 19,3</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,85; 12,43</t>
+          <t>3,57; 12,16</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,84; 6,48</t>
+          <t>2,57; 6,56</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>10,74; 16,11</t>
+          <t>10,53; 16,06</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,15; 14,59</t>
+          <t>10,11; 14,51</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,0; 5,45</t>
+          <t>3,12; 5,68</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>12,58; 16,94</t>
+          <t>12,43; 16,46</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,63; 12,52</t>
+          <t>6,33; 12,45</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,88; 6,96</t>
+          <t>3,15; 7,35</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>13,45; 20,75</t>
+          <t>13,03; 20,19</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,58; 12,42</t>
+          <t>7,48; 12,48</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,02; 7,06</t>
+          <t>3,02; 7,37</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>12,56; 19,42</t>
+          <t>12,36; 19,05</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,15; 13,18</t>
+          <t>9,22; 13,19</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,41; 6,3</t>
+          <t>3,44; 6,38</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>13,71; 18,52</t>
+          <t>13,57; 18,67</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8,85; 12,13</t>
+          <t>9,04; 12,23</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,01; 4,62</t>
+          <t>1,28; 5,02</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>12,7; 20,57</t>
+          <t>12,5; 20,45</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7,04; 12,38</t>
+          <t>7,19; 12,49</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,01; 7,24</t>
+          <t>3,01; 7,32</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>11,14; 18,52</t>
+          <t>11,71; 19,18</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,87; 11,63</t>
+          <t>2,96; 11,73</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,53; 5,3</t>
+          <t>2,41; 5,28</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>12,98; 18,16</t>
+          <t>12,96; 18,38</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4,31; 10,97</t>
+          <t>4,23; 10,85</t>
         </is>
       </c>
     </row>
@@ -1338,17 +1338,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,05; 5,52</t>
+          <t>0,9; 5,53</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>12,76; 21,5</t>
+          <t>12,68; 21,24</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7,82; 14,33</t>
+          <t>8,0; 14,34</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1358,27 +1358,27 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>11,45; 19,59</t>
+          <t>11,63; 19,49</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,35; 14,0</t>
+          <t>9,62; 14,18</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,63; 7,19</t>
+          <t>3,48; 7,04</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>13,19; 19,19</t>
+          <t>12,91; 19,18</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>9,38; 13,17</t>
+          <t>9,39; 13,38</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>3,5; 4,89</t>
+          <t>3,46; 4,88</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>14,4; 17,1</t>
+          <t>14,5; 17,0</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8,15; 11,9</t>
+          <t>8,29; 11,96</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,81; 5,24</t>
+          <t>3,83; 5,28</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>13,35; 15,83</t>
+          <t>13,45; 15,87</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,7; 17,92</t>
+          <t>9,65; 16,98</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,88; 4,89</t>
+          <t>3,83; 4,83</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>14,18; 15,97</t>
+          <t>14,21; 16,12</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>9,83; 14,88</t>
+          <t>9,7; 14,15</t>
         </is>
       </c>
     </row>
@@ -1543,7 +1543,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con temperatura insuficiente</t>
+          <t>Población con temperatura insuficiente, en verano o en invierno, en la vivienda (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1750,47 +1750,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>11333; 28500</t>
+          <t>11657; 29711</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>52213; 84872</t>
+          <t>51715; 84110</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>24602; 73775</t>
+          <t>23913; 75141</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12580; 30741</t>
+          <t>12748; 30086</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>42222; 71565</t>
+          <t>42139; 70722</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12979; 46711</t>
+          <t>13386; 46692</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27473; 51551</t>
+          <t>27209; 52841</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>101871; 144294</t>
+          <t>104065; 144314</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>47061; 104616</t>
+          <t>46338; 101119</t>
         </is>
       </c>
     </row>
@@ -1913,47 +1913,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>25781; 52637</t>
+          <t>23369; 51743</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>80311; 116883</t>
+          <t>77712; 115330</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>37557; 74065</t>
+          <t>37780; 75138</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11473; 27643</t>
+          <t>11517; 29315</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>79429; 112886</t>
+          <t>79215; 113030</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>52274; 272118</t>
+          <t>53434; 274903</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>40958; 71286</t>
+          <t>41891; 73923</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>168099; 220700</t>
+          <t>169276; 221565</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>104211; 353210</t>
+          <t>103892; 356571</t>
         </is>
       </c>
     </row>
@@ -2076,47 +2076,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>18914; 41283</t>
+          <t>20011; 41901</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>72139; 109924</t>
+          <t>71924; 109632</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>53808; 85518</t>
+          <t>53885; 85205</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>19149; 41865</t>
+          <t>19691; 42914</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>66164; 100037</t>
+          <t>68018; 100754</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>41368; 71555</t>
+          <t>40122; 69786</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>43047; 73665</t>
+          <t>44163; 75476</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>147862; 198732</t>
+          <t>148849; 197533</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>103199; 148346</t>
+          <t>102659; 147452</t>
         </is>
       </c>
     </row>
@@ -2239,47 +2239,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>14621; 35346</t>
+          <t>13856; 34432</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>82042; 123211</t>
+          <t>84643; 124677</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>25327; 110377</t>
+          <t>31676; 107936</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>17491; 39924</t>
+          <t>15862; 40402</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>69685; 104579</t>
+          <t>68347; 104234</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>72389; 104024</t>
+          <t>72065; 103449</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>36882; 67058</t>
+          <t>38362; 69970</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>162891; 219370</t>
+          <t>160935; 213184</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>90152; 200400</t>
+          <t>101307; 199324</t>
         </is>
       </c>
     </row>
@@ -2402,47 +2402,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>12371; 29870</t>
+          <t>13511; 31567</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>64263; 99188</t>
+          <t>62267; 96483</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>42556; 69731</t>
+          <t>41961; 70061</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>13524; 31624</t>
+          <t>13505; 33020</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>62425; 96471</t>
+          <t>61434; 94658</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>50109; 72204</t>
+          <t>50518; 72275</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>29918; 55296</t>
+          <t>30172; 55995</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>133617; 180546</t>
+          <t>132240; 181991</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>98181; 134542</t>
+          <t>100226; 135613</t>
         </is>
       </c>
     </row>
@@ -2565,47 +2565,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3126; 14322</t>
+          <t>3953; 15558</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>42475; 68786</t>
+          <t>41792; 68375</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>25923; 45583</t>
+          <t>26474; 45984</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>10662; 25638</t>
+          <t>10652; 25907</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>42077; 69948</t>
+          <t>44244; 72438</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>17463; 70728</t>
+          <t>17986; 71367</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>16780; 35205</t>
+          <t>16016; 35028</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>92408; 129345</t>
+          <t>92312; 130888</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>42104; 107087</t>
+          <t>41263; 105973</t>
         </is>
       </c>
     </row>
@@ -2728,47 +2728,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2627; 13782</t>
+          <t>2244; 13829</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>32800; 55256</t>
+          <t>32593; 54575</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>22113; 40525</t>
+          <t>22608; 40535</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>17509; 37310</t>
+          <t>17511; 37308</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>45808; 78405</t>
+          <t>46554; 77998</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>39803; 59617</t>
+          <t>40952; 60394</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>23191; 45906</t>
+          <t>22215; 44958</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>86683; 126131</t>
+          <t>84832; 126054</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>66467; 93327</t>
+          <t>66531; 94795</t>
         </is>
       </c>
     </row>
@@ -2891,47 +2891,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>120094; 167483</t>
+          <t>118571; 167116</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>488903; 580562</t>
+          <t>492038; 577072</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>281962; 411882</t>
+          <t>286686; 413730</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>135657; 186311</t>
+          <t>136385; 187873</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>473334; 561205</t>
+          <t>476803; 562513</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>360218; 665407</t>
+          <t>358228; 630368</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>270685; 341272</t>
+          <t>267675; 337458</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>984256; 1108322</t>
+          <t>986040; 1118529</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>705061; 1067406</t>
+          <t>695414; 1014653</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/Viv_Temp_insuf-Edad-trans_dic.xlsx
+++ b/data/trans_dic/Viv_Temp_insuf-Edad-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con temperatura insuficiente, en verano o en invierno, en la vivienda (tasa de respuesta: 100,0%)</t>
+          <t>Población con temperatura insuficiente, en verano o en invierno, en la vivienda (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>36,61%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>45,59%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>40,83%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,2; 18,04</t>
+          <t>29,25; 44,06</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,04; 15,5</t>
+          <t>38,64; 53,26</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,93; 15,47</t>
+          <t>35,51; 46,03</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>39,72%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>37,43%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>38,55%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>10,4; 18,97</t>
+          <t>34,2; 45,76</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10,09; 16,33</t>
+          <t>33,07; 42,16</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11,43; 16,67</t>
+          <t>34,97; 42,15</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>37,49%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>38,1%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>37,79%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11,05; 16,9</t>
+          <t>33,73; 41,88</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9,46; 13,91</t>
+          <t>34,63; 41,53</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10,63; 14,43</t>
+          <t>35,18; 40,71</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>38,3%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>43,93%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>41,18%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,96; 15,0</t>
+          <t>34,73; 42,19</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11,97; 16,07</t>
+          <t>40,94; 46,88</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11,58; 14,82</t>
+          <t>38,87; 43,77</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>38,16%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>42,09%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>40,13%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8,3; 13,13</t>
+          <t>34,58; 42,23</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>10,53; 14,58</t>
+          <t>39,06; 45,35</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9,87; 13,09</t>
+          <t>37,44; 42,46</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>39,41%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>40,35%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>39,9%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7,91; 13,43</t>
+          <t>35,26; 43,48</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9,01; 13,43</t>
+          <t>36,55; 43,39</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9,03; 12,52</t>
+          <t>37,37; 42,73</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>42,72%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>39,3%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>40,67%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>8,75; 15,61</t>
+          <t>38,1; 47,52</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>9,74; 14,86</t>
+          <t>35,99; 42,68</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10,26; 14,29</t>
+          <t>37,64; 43,38</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>38,65%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>40,95%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>39,83%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>11,04; 13,64</t>
+          <t>36,8; 40,63</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>11,2; 13,17</t>
+          <t>39,47; 42,41</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11,46; 13,01</t>
+          <t>38,64; 40,93</t>
         </is>
       </c>
     </row>
@@ -978,7 +978,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con temperatura insuficiente, en verano o en invierno, en la vivienda (tasa de respuesta: 100,0%)</t>
+          <t>Población con temperatura insuficiente, en verano o en invierno, en la vivienda (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1037,17 +1037,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>68</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>95</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>163</t>
         </is>
       </c>
     </row>
@@ -1060,17 +1060,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>49283</t>
+          <t>149283</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>35981</t>
+          <t>165257</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>85265</t>
+          <t>314540</t>
         </is>
       </c>
     </row>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>29375; 73564</t>
+          <t>119277; 179666</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>21912; 56190</t>
+          <t>140059; 193076</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>61108; 119157</t>
+          <t>273564; 354537</t>
         </is>
       </c>
     </row>
@@ -1110,17 +1110,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>124</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>171</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>295</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>68352</t>
+          <t>188780</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>65597</t>
+          <t>187817</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>133950</t>
+          <t>376597</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>49586; 90475</t>
+          <t>162545; 217461</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>50620; 81933</t>
+          <t>165926; 211553</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>111868; 163178</t>
+          <t>341678; 411752</t>
         </is>
       </c>
     </row>
@@ -1183,17 +1183,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>208</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>308</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>516</t>
         </is>
       </c>
     </row>
@@ -1206,17 +1206,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>86053</t>
+          <t>231966</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>71990</t>
+          <t>236798</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>158043</t>
+          <t>468765</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>68600; 104935</t>
+          <t>208704; 259148</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>58966; 86712</t>
+          <t>215217; 258099</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>132220; 179480</t>
+          <t>436296; 504889</t>
         </is>
       </c>
     </row>
@@ -1256,17 +1256,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>246</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>470</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>716</t>
         </is>
       </c>
     </row>
@@ -1279,17 +1279,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>86273</t>
+          <t>268342</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>102098</t>
+          <t>323396</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>188371</t>
+          <t>591738</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>69806; 105092</t>
+          <t>243316; 295622</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>88189; 118383</t>
+          <t>301427; 345103</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>166466; 213042</t>
+          <t>558483; 628877</t>
         </is>
       </c>
     </row>
@@ -1329,17 +1329,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>255</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>394</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>649</t>
         </is>
       </c>
     </row>
@@ -1352,17 +1352,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>65132</t>
+          <t>231584</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>74843</t>
+          <t>255998</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>139975</t>
+          <t>487581</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>50590; 80020</t>
+          <t>209855; 256244</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>64099; 88799</t>
+          <t>237520; 275783</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>120186; 159471</t>
+          <t>454830; 515858</t>
         </is>
       </c>
     </row>
@@ -1402,17 +1402,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>228</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>313</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>541</t>
         </is>
       </c>
     </row>
@@ -1425,17 +1425,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>42077</t>
+          <t>160419</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>48891</t>
+          <t>177205</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>90968</t>
+          <t>337624</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>32182; 54683</t>
+          <t>143542; 177012</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>39576; 58963</t>
+          <t>160516; 190557</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>76450; 105944</t>
+          <t>316259; 361559</t>
         </is>
       </c>
     </row>
@@ -1475,17 +1475,17 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>192</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>317</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>509</t>
         </is>
       </c>
     </row>
@@ -1498,17 +1498,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>37106</t>
+          <t>132512</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>56728</t>
+          <t>182605</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>93834</t>
+          <t>315118</t>
         </is>
       </c>
     </row>
@@ -1521,17 +1521,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>27140; 48427</t>
+          <t>118190; 147406</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>45266; 69020</t>
+          <t>167217; 198280</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>79493; 110758</t>
+          <t>291600; 336124</t>
         </is>
       </c>
     </row>
@@ -1548,17 +1548,17 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>1321</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>2068</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>981</t>
+          <t>3389</t>
         </is>
       </c>
     </row>
@@ -1571,17 +1571,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>434277</t>
+          <t>1362887</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>456129</t>
+          <t>1529076</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>890406</t>
+          <t>2891963</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>390005; 481850</t>
+          <t>1297904; 1432729</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>418692; 492341</t>
+          <t>1473565; 1583441</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>833004; 945539</t>
+          <t>2805564; 2971348</t>
         </is>
       </c>
     </row>
